--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486867_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486867_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5277</v>
+        <v>5.0325</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0211</v>
+        <v>6.4666</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4934</v>
+        <v>-1.4341</v>
       </c>
       <c r="G2" t="n">
         <v>0.526</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3612</v>
+        <v>0.866</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7246</v>
+        <v>-0.279</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0857</v>
+        <v>1.145</v>
       </c>
       <c r="V2" t="n">
         <v>4.2566</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7857</v>
+        <v>2.3631</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1209</v>
+        <v>3.5204</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3351</v>
+        <v>-1.1573</v>
       </c>
       <c r="G3" t="n">
         <v>-2.3727</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5055</v>
+        <v>1.0829</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6701</v>
+        <v>0.0696</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8354</v>
+        <v>1.0133</v>
       </c>
       <c r="V3" t="n">
         <v>4.4743</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0712</v>
+        <v>1.9205</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4426</v>
+        <v>3.4697</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3714</v>
+        <v>-1.5492</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3098</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1407</v>
+        <v>0.99</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>-0.0001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.168</v>
+        <v>0.9901</v>
       </c>
       <c r="V4" t="n">
         <v>0.8295</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4837</v>
+        <v>-0.3552</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4795</v>
+        <v>0.505</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0043</v>
+        <v>-0.8602</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8852</v>
+        <v>0.1117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07770000000000001</v>
+        <v>2.4298</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9629</v>
+        <v>-2.3181</v>
       </c>
       <c r="J5" t="n">
-        <v>2.066</v>
+        <v>1.9425</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3821</v>
+        <v>2.7057</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.7633</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9513</v>
+        <v>-1.8308</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3044</v>
+        <v>-0.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6468</v>
+        <v>-1.5549</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.73</v>
+        <v>0.1491</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.527</v>
+        <v>-0.2054</v>
       </c>
       <c r="U5" t="n">
-        <v>1.257</v>
+        <v>0.3546</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5989</v>
+        <v>-0.3922</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1413</v>
+        <v>1.3777</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7402</v>
+        <v>-1.7698</v>
       </c>
       <c r="G6" t="n">
         <v>-0.28</v>
@@ -922,13 +922,13 @@
         <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4491</v>
+        <v>0.6558</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4534</v>
+        <v>-0.217</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9024</v>
+        <v>0.8728</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1786</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.4253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1912</v>
+        <v>-0.2431</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9195</v>
+        <v>-0.1821</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1117</v>
+        <v>-0.8852</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4298</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3181</v>
+        <v>-0.9629</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9425</v>
+        <v>2.066</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7057</v>
+        <v>1.3821</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7633</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8308</v>
+        <v>-2.9513</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2759</v>
+        <v>-1.3044</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5549</v>
+        <v>-1.6468</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R7" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.224</v>
+        <v>0.7885</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5192</v>
+        <v>-0.2906</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2953</v>
+        <v>1.0792</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6887</v>
+        <v>-1.3312</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3653</v>
+        <v>-1.1561</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3234</v>
+        <v>-0.1751</v>
       </c>
       <c r="G8" t="n">
         <v>1.5054</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5985</v>
+        <v>-0.2411</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>-0.1202</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2692</v>
+        <v>-0.121</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1314</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4594</v>
+        <v>-3.041</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7517</v>
+        <v>-3.3332</v>
       </c>
       <c r="F9" t="n">
         <v>0.2922</v>
@@ -1156,10 +1156,10 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4261</v>
+        <v>-0.0077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.527</v>
+        <v>-0.1086</v>
       </c>
       <c r="U9" t="n">
         <v>0.1008</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6898</v>
+        <v>-3.4649</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2115</v>
+        <v>-1.8977</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4783</v>
+        <v>-1.5672</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6619</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4118</v>
+        <v>-0.1869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5192</v>
+        <v>-0.2054</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1074</v>
+        <v>0.0185</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2126</v>
+        <v>-4.1672</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2508</v>
+        <v>-2.1462</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9618</v>
+        <v>-2.0211</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8673999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3185</v>
+        <v>-0.2731</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.122</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2042</v>
+        <v>-6.1613</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0489</v>
+        <v>-1.095</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1553</v>
+        <v>-5.0663</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4903</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>1.822</v>
+        <v>0.8649</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5069</v>
+        <v>0.4609</v>
       </c>
       <c r="U12" t="n">
-        <v>0.315</v>
+        <v>0.404</v>
       </c>
       <c r="V12" t="n">
         <v>-4.1252</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.681</v>
+        <v>-10.0222</v>
       </c>
       <c r="E13" t="n">
-        <v>4.809400000000001</v>
+        <v>5.468099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.4905</v>
+        <v>-15.4902</v>
       </c>
       <c r="G13" t="n">
         <v>-9.812899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4063</v>
+        <v>-0.4063000000000004</v>
       </c>
       <c r="I13" t="n">
         <v>-9.406599999999999</v>
@@ -1447,7 +1447,7 @@
         <v>10.5457</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4832</v>
+        <v>6.483199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-26.842</v>
@@ -1468,13 +1468,13 @@
         <v>10.2671</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0296</v>
+        <v>4.688400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.705800000000001</v>
+        <v>-1.047</v>
       </c>
       <c r="U13" t="n">
-        <v>5.7351</v>
+        <v>5.735300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.342999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6786</v>
+        <v>7.1327</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0803</v>
+        <v>6.1839</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5983</v>
+        <v>0.9488</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2707</v>
+        <v>2.5602</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0054</v>
+        <v>2.005</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2653</v>
+        <v>0.5552</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9875</v>
+        <v>4.6984</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7252</v>
+        <v>3.4489</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2623</v>
+        <v>1.2495</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7168</v>
+        <v>-2.1382</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7198</v>
+        <v>-1.4439</v>
       </c>
       <c r="O14" t="n">
-        <v>0.003</v>
+        <v>-0.6943</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9015</v>
+        <v>3.0801</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3669</v>
+        <v>-0.5938</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0468</v>
+        <v>-1.0811</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4136</v>
+        <v>0.4873</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3716</v>
+        <v>3.3182</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3716</v>
+        <v>3.7987</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9775</v>
+        <v>7.1015</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0793</v>
+        <v>4.4527</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8983</v>
+        <v>2.6489</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5602</v>
+        <v>4.2707</v>
       </c>
       <c r="H15" t="n">
-        <v>2.005</v>
+        <v>1.0054</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5552</v>
+        <v>3.2653</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6984</v>
+        <v>5.9875</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4489</v>
+        <v>2.7252</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2495</v>
+        <v>3.2623</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1382</v>
+        <v>-1.7168</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4439</v>
+        <v>-1.7198</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6943</v>
+        <v>0.003</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0801</v>
+        <v>3.9015</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7489</v>
+        <v>-0.2102</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1857</v>
+        <v>-0.6744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4368</v>
+        <v>0.4641</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3182</v>
+        <v>0.3716</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7987</v>
+        <v>0.3716</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.506</v>
+        <v>5.9263</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4295</v>
+        <v>5.3248</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0766</v>
+        <v>0.6014</v>
       </c>
       <c r="G16" t="n">
         <v>4.9707</v>
@@ -1702,13 +1702,13 @@
         <v>3.4908</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1341</v>
+        <v>-0.7139</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8758</v>
+        <v>-0.9805</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2583</v>
+        <v>0.2665</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7381</v>
+        <v>3.6771</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8693</v>
+        <v>1.66</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8688</v>
+        <v>2.0171</v>
       </c>
       <c r="G17" t="n">
         <v>2.8521</v>
@@ -1780,13 +1780,13 @@
         <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2228</v>
+        <v>-0.2838</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4147</v>
+        <v>-0.6239</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1919</v>
+        <v>0.3401</v>
       </c>
       <c r="V17" t="n">
         <v>0.6982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7492</v>
+        <v>0.7998</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0265</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="G18" t="n">
         <v>0.3397</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2065</v>
+        <v>-0.1559</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1976</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0089</v>
+        <v>0.0417</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3984</v>
+        <v>-0.1142</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3519</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7503</v>
+        <v>-0.78</v>
       </c>
       <c r="G19" t="n">
         <v>-0.584</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0198</v>
+        <v>0.2644</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3294</v>
+        <v>-0.0156</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.941</v>
+        <v>-2.8998</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8824</v>
+        <v>-2.8415</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0586</v>
+        <v>-0.0583</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6973</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7397</v>
+        <v>-0.7917</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9576</v>
+        <v>0.0341</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.619</v>
+        <v>1.8358</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0389</v>
+        <v>0.1786</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6579</v>
+        <v>1.6572</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0783</v>
+        <v>-2.5934</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7786</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2997</v>
+        <v>-1.6231</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.4908</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2437</v>
+        <v>-0.2306</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2635</v>
+        <v>-0.6937</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0198</v>
+        <v>0.4631</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.117</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0427</v>
+        <v>-2.9114</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2599</v>
+        <v>-0.8824</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2172</v>
+        <v>-2.0289</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-2.6973</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7917</v>
+        <v>-0.7397</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0341</v>
+        <v>-1.9576</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8358</v>
+        <v>-0.619</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1786</v>
+        <v>0.0389</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6572</v>
+        <v>-0.6579</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5934</v>
+        <v>-2.0783</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.7786</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6231</v>
+        <v>-1.2997</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4908</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3734</v>
+        <v>-0.2141</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1121</v>
+        <v>-0.2635</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7387</v>
+        <v>0.0494</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.117</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6872</v>
+        <v>-5.4344</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4642</v>
+        <v>0.5688</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.1514</v>
+        <v>-6.0032</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9671999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>1.6427</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9706</v>
+        <v>-0.7178</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7169</v>
+        <v>-0.6123</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2537</v>
+        <v>-0.1055</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3654</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.6808</v>
+        <v>11.3783</v>
       </c>
       <c r="E25" t="n">
-        <v>15.4904</v>
+        <v>15.4903</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.8094</v>
+        <v>-4.1119</v>
       </c>
       <c r="G25" t="n">
         <v>9.813000000000001</v>
@@ -2392,7 +2392,7 @@
         <v>-10.5457</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.4833</v>
+        <v>-6.483300000000001</v>
       </c>
       <c r="P25" t="n">
         <v>9.240299999999998</v>
@@ -2404,13 +2404,13 @@
         <v>19.5073</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.0294</v>
+        <v>-3.3322</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.7353</v>
+        <v>-5.7354</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7058</v>
+        <v>2.403</v>
       </c>
       <c r="V25" t="n">
         <v>-4.3428</v>
